--- a/src/test/resources/TestLoginData.xlsx
+++ b/src/test/resources/TestLoginData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="61">
   <si>
     <t>STT</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>http://localhost:8080/home/index;jsessionid=9AC583D893069A71CBA40342CD441690</t>
+  </si>
+  <si>
+    <t>http://localhost:8080/home/index;jsessionid=EABCB6ABD2A446E43C0EEAF6E143D28F</t>
+  </si>
+  <si>
+    <t>http://localhost:8080/home/index;jsessionid=CB32D2B4515D1704ED00A90FA13FA2D0</t>
   </si>
 </sst>
 </file>
@@ -663,7 +669,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>29</v>
@@ -686,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>29</v>

--- a/src/test/resources/TestLoginData.xlsx
+++ b/src/test/resources/TestLoginData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="63">
   <si>
     <t>STT</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>http://localhost:8080/home/index;jsessionid=CB32D2B4515D1704ED00A90FA13FA2D0</t>
+  </si>
+  <si>
+    <t>http://localhost:8080/home/index;jsessionid=FB6C63AB4A7C5563C93A8390E3866BE6</t>
+  </si>
+  <si>
+    <t>http://localhost:8080/home/index;jsessionid=27454B60D98F8D36C5178355756BDCA3</t>
   </si>
 </sst>
 </file>
@@ -669,7 +675,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>29</v>
@@ -692,7 +698,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>29</v>
